--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6800" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6799" uniqueCount="707">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1290,10 +1290,10 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>Seitenlokalisation (OPS-Seitenzusatz R/L/B)</t>
+  </si>
+  <si>
+    <t>Seitenangabe bei paarigen Organen und OPS-Codes mit Seitenzusatzpflicht über die Basisprofil-Extension seitenlokalisation (R/L/B). Das oBDS sieht am OP kein eigenes Seitenfeld vor; führend ist der OPS-Seitenzusatz.</t>
   </si>
   <si>
     <t>Procedure.code.coding:ops.system</t>
@@ -11225,7 +11225,7 @@
         <v>406</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11252,9 +11252,7 @@
       <c r="M81" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="N81" t="s" s="2">
-        <v>109</v>
-      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$237</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8762" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8803" uniqueCount="833">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1486,6 +1486,9 @@
   </si>
   <si>
     <t>Procedure.code.coding.extension.value[x].code</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
@@ -2017,6 +2020,22 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding</t>
@@ -2888,7 +2907,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO236"/>
+  <dimension ref="A1:AO237"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -5248,7 +5267,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>117</v>
@@ -5480,7 +5499,7 @@
         <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>101</v>
@@ -14005,7 +14024,7 @@
         <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>117</v>
@@ -14354,7 +14373,7 @@
         <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>117</v>
@@ -14584,7 +14603,7 @@
         <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>101</v>
@@ -14816,7 +14835,7 @@
         <v>80</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>117</v>
@@ -14935,7 +14954,7 @@
         <v>89</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>101</v>
@@ -15052,7 +15071,7 @@
         <v>89</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>101</v>
@@ -15109,7 +15128,9 @@
       <c r="M105" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N105" s="2"/>
+      <c r="N105" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="O105" t="s" s="2">
         <v>248</v>
       </c>
@@ -15169,7 +15190,7 @@
         <v>89</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>101</v>
@@ -15192,10 +15213,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15226,7 +15247,9 @@
       <c r="M106" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N106" s="2"/>
+      <c r="N106" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="O106" t="s" s="2">
         <v>255</v>
       </c>
@@ -15286,7 +15309,7 @@
         <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>101</v>
@@ -15309,10 +15332,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15405,7 +15428,7 @@
         <v>89</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>101</v>
@@ -15428,10 +15451,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15457,7 +15480,7 @@
         <v>130</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>231</v>
@@ -15473,7 +15496,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>78</v>
@@ -15524,7 +15547,7 @@
         <v>89</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>101</v>
@@ -15547,10 +15570,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15576,10 +15599,10 @@
         <v>103</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>241</v>
@@ -15641,7 +15664,7 @@
         <v>89</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>101</v>
@@ -15650,7 +15673,7 @@
         <v>78</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -15664,10 +15687,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15693,12 +15716,14 @@
         <v>164</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M110" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N110" s="2"/>
+      <c r="N110" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="O110" t="s" s="2">
         <v>248</v>
       </c>
@@ -15713,7 +15738,7 @@
         <v>78</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>78</v>
@@ -15758,16 +15783,16 @@
         <v>89</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -15781,10 +15806,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15815,7 +15840,9 @@
       <c r="M111" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N111" s="2"/>
+      <c r="N111" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="O111" t="s" s="2">
         <v>255</v>
       </c>
@@ -15875,7 +15902,7 @@
         <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>101</v>
@@ -15898,10 +15925,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15994,7 +16021,7 @@
         <v>89</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>101</v>
@@ -16017,7 +16044,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>437</v>
@@ -16086,7 +16113,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>78</v>
@@ -16136,7 +16163,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>446</v>
@@ -16251,7 +16278,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>448</v>
@@ -16368,10 +16395,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16487,10 +16514,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16604,10 +16631,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16721,10 +16748,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16838,10 +16865,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16957,10 +16984,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17076,14 +17103,14 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -17102,13 +17129,13 @@
         <v>90</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17159,7 +17186,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>89</v>
@@ -17180,21 +17207,21 @@
         <v>78</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17306,10 +17333,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17423,10 +17450,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17452,13 +17479,13 @@
         <v>103</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17508,7 +17535,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17517,7 +17544,7 @@
         <v>89</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>101</v>
@@ -17540,10 +17567,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17569,13 +17596,13 @@
         <v>130</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17604,10 +17631,10 @@
         <v>146</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>78</v>
@@ -17625,7 +17652,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17657,10 +17684,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17686,13 +17713,13 @@
         <v>343</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17742,7 +17769,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17774,10 +17801,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17803,13 +17830,13 @@
         <v>103</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17859,7 +17886,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17891,10 +17918,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17917,16 +17944,16 @@
         <v>90</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17976,7 +18003,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17997,21 +18024,21 @@
         <v>78</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18123,10 +18150,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18240,10 +18267,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18269,13 +18296,13 @@
         <v>103</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18325,7 +18352,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18334,7 +18361,7 @@
         <v>89</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>101</v>
@@ -18357,10 +18384,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18386,13 +18413,13 @@
         <v>130</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18421,10 +18448,10 @@
         <v>146</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>78</v>
@@ -18442,7 +18469,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18474,10 +18501,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18503,13 +18530,13 @@
         <v>343</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18559,7 +18586,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18591,10 +18618,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18620,13 +18647,13 @@
         <v>103</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18676,7 +18703,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18708,10 +18735,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18737,13 +18764,13 @@
         <v>208</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18781,17 +18808,17 @@
         <v>78</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AC136" s="2"/>
       <c r="AD136" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18812,24 +18839,24 @@
         <v>78</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>78</v>
@@ -18854,13 +18881,13 @@
         <v>208</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18910,7 +18937,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18928,27 +18955,27 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>78</v>
@@ -18970,16 +18997,16 @@
         <v>90</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -19029,7 +19056,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -19050,21 +19077,21 @@
         <v>78</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19087,13 +19114,13 @@
         <v>90</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19144,7 +19171,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -19168,7 +19195,7 @@
         <v>78</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>78</v>
@@ -19176,10 +19203,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19202,13 +19229,13 @@
         <v>90</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19259,7 +19286,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19283,7 +19310,7 @@
         <v>78</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>78</v>
@@ -19291,10 +19318,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19317,13 +19344,13 @@
         <v>90</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19374,7 +19401,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19395,7 +19422,7 @@
         <v>78</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>78</v>
@@ -19406,10 +19433,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19521,10 +19548,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19638,14 +19665,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -19667,10 +19694,10 @@
         <v>109</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>112</v>
@@ -19725,7 +19752,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -19757,10 +19784,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19786,14 +19813,14 @@
         <v>277</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -19821,10 +19848,10 @@
         <v>154</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>78</v>
@@ -19842,7 +19869,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19863,21 +19890,21 @@
         <v>78</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19900,17 +19927,17 @@
         <v>90</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -19959,7 +19986,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>89</v>
@@ -19980,21 +20007,21 @@
         <v>78</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20017,17 +20044,17 @@
         <v>78</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>78</v>
@@ -20076,7 +20103,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20108,10 +20135,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20134,17 +20161,17 @@
         <v>90</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>78</v>
@@ -20193,7 +20220,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20217,7 +20244,7 @@
         <v>78</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>78</v>
@@ -20225,10 +20252,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20254,13 +20281,13 @@
         <v>277</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20289,10 +20316,10 @@
         <v>154</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>78</v>
@@ -20310,7 +20337,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20331,10 +20358,10 @@
         <v>78</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>78</v>
@@ -20342,10 +20369,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20368,16 +20395,16 @@
         <v>90</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20427,7 +20454,7 @@
         <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20448,10 +20475,10 @@
         <v>78</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>78</v>
@@ -20459,10 +20486,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20488,13 +20515,13 @@
         <v>277</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20523,10 +20550,10 @@
         <v>154</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>78</v>
@@ -20544,7 +20571,7 @@
         <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -20571,15 +20598,15 @@
         <v>78</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20691,10 +20718,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20808,12 +20835,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="C154" s="2"/>
+      <c r="C154" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="D154" t="s" s="2">
         <v>78</v>
       </c>
@@ -20822,32 +20851,28 @@
         <v>79</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>142</v>
+        <v>647</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>283</v>
+        <v>648</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="N154" s="2"/>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>78</v>
       </c>
@@ -20883,17 +20908,19 @@
         <v>78</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AC154" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD154" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20905,7 +20932,7 @@
         <v>78</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>78</v>
@@ -20920,19 +20947,17 @@
         <v>78</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="C155" t="s" s="2">
-        <v>647</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
         <v>78</v>
       </c>
@@ -20941,7 +20966,7 @@
         <v>79</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>90</v>
@@ -20956,10 +20981,10 @@
         <v>142</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>405</v>
+        <v>283</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>406</v>
+        <v>284</v>
       </c>
       <c r="N155" t="s" s="2">
         <v>285</v>
@@ -21002,16 +21027,14 @@
         <v>78</v>
       </c>
       <c r="AB155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="AC155" s="2"/>
       <c r="AD155" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE155" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF155" t="s" s="2">
         <v>287</v>
@@ -21044,14 +21067,16 @@
         <v>288</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="C156" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="C156" t="s" s="2">
+        <v>653</v>
+      </c>
       <c r="D156" t="s" s="2">
         <v>78</v>
       </c>
@@ -21063,25 +21088,29 @@
         <v>89</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>104</v>
+        <v>405</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N156" s="2"/>
-      <c r="O156" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P156" t="s" s="2">
         <v>78</v>
       </c>
@@ -21129,19 +21158,19 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>78</v>
@@ -21156,26 +21185,26 @@
         <v>78</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>78</v>
@@ -21187,17 +21216,15 @@
         <v>78</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>78</v>
@@ -21234,31 +21261,31 @@
         <v>78</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>78</v>
@@ -21276,48 +21303,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>78</v>
       </c>
@@ -21326,7 +21351,7 @@
         <v>78</v>
       </c>
       <c r="S158" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="T158" t="s" s="2">
         <v>78</v>
@@ -21353,31 +21378,31 @@
         <v>78</v>
       </c>
       <c r="AB158" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC158" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE158" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>78</v>
@@ -21392,15 +21417,15 @@
         <v>78</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21408,7 +21433,7 @@
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G159" t="s" s="2">
         <v>89</v>
@@ -21423,18 +21448,20 @@
         <v>90</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O159" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
       </c>
@@ -21443,7 +21470,7 @@
         <v>78</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>78</v>
@@ -21482,7 +21509,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21509,15 +21536,15 @@
         <v>78</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21525,7 +21552,7 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>89</v>
@@ -21540,18 +21567,18 @@
         <v>90</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>78</v>
       </c>
@@ -21599,7 +21626,7 @@
         <v>78</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -21626,15 +21653,15 @@
         <v>78</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21642,13 +21669,13 @@
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G161" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>78</v>
@@ -21657,17 +21684,17 @@
         <v>90</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>78</v>
@@ -21716,7 +21743,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -21743,15 +21770,15 @@
         <v>78</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21774,19 +21801,17 @@
         <v>90</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>78</v>
@@ -21835,7 +21860,7 @@
         <v>78</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21862,15 +21887,15 @@
         <v>78</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21893,19 +21918,19 @@
         <v>90</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>78</v>
@@ -21954,7 +21979,7 @@
         <v>78</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -21981,15 +22006,15 @@
         <v>78</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22003,7 +22028,7 @@
         <v>89</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>78</v>
@@ -22012,18 +22037,20 @@
         <v>90</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>664</v>
+        <v>307</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>665</v>
+        <v>308</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="O164" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>78</v>
       </c>
@@ -22047,11 +22074,13 @@
         <v>78</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y164" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z164" t="s" s="2">
-        <v>667</v>
+        <v>78</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>78</v>
@@ -22069,7 +22098,7 @@
         <v>78</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>663</v>
+        <v>311</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -22087,7 +22116,7 @@
         <v>78</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>668</v>
+        <v>78</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>78</v>
@@ -22096,10 +22125,10 @@
         <v>78</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
         <v>669</v>
       </c>
@@ -22118,24 +22147,26 @@
         <v>89</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>104</v>
+        <v>670</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N165" s="2"/>
+        <v>671</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>672</v>
+      </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>78</v>
@@ -22160,13 +22191,11 @@
         <v>78</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y165" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
-        <v>78</v>
+        <v>673</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>78</v>
@@ -22184,7 +22213,7 @@
         <v>78</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>106</v>
+        <v>669</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22196,13 +22225,13 @@
         <v>78</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK165" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>78</v>
+        <v>674</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>78</v>
@@ -22216,21 +22245,21 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>78</v>
@@ -22242,17 +22271,15 @@
         <v>78</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N166" s="2"/>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>78</v>
@@ -22289,31 +22316,31 @@
         <v>78</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>78</v>
@@ -22333,14 +22360,14 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
@@ -22356,23 +22383,21 @@
         <v>78</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>672</v>
+        <v>110</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>673</v>
+        <v>111</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>78</v>
       </c>
@@ -22408,19 +22433,19 @@
         <v>78</v>
       </c>
       <c r="AB167" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC167" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD167" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE167" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22432,7 +22457,7 @@
         <v>78</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>78</v>
@@ -22447,15 +22472,15 @@
         <v>78</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22466,7 +22491,7 @@
         <v>79</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>78</v>
@@ -22475,19 +22500,23 @@
         <v>78</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>104</v>
+        <v>678</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N168" s="2"/>
-      <c r="O168" s="2"/>
+        <v>679</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O168" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P168" t="s" s="2">
         <v>78</v>
       </c>
@@ -22535,19 +22564,19 @@
         <v>78</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>78</v>
@@ -22562,26 +22591,26 @@
         <v>78</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>78</v>
@@ -22593,17 +22622,15 @@
         <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N169" s="2"/>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>78</v>
@@ -22640,31 +22667,31 @@
         <v>78</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>78</v>
@@ -22682,48 +22709,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H170" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>78</v>
       </c>
@@ -22732,7 +22757,7 @@
         <v>78</v>
       </c>
       <c r="S170" t="s" s="2">
-        <v>677</v>
+        <v>78</v>
       </c>
       <c r="T170" t="s" s="2">
         <v>78</v>
@@ -22759,31 +22784,31 @@
         <v>78</v>
       </c>
       <c r="AB170" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC170" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE170" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>78</v>
@@ -22798,15 +22823,15 @@
         <v>78</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="171" hidden="true">
+    <row r="171">
       <c r="A171" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22820,7 +22845,7 @@
         <v>89</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>78</v>
@@ -22829,18 +22854,20 @@
         <v>90</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O171" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O171" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P171" t="s" s="2">
         <v>78</v>
       </c>
@@ -22849,7 +22876,7 @@
         <v>78</v>
       </c>
       <c r="S171" t="s" s="2">
-        <v>78</v>
+        <v>683</v>
       </c>
       <c r="T171" t="s" s="2">
         <v>78</v>
@@ -22888,7 +22915,7 @@
         <v>78</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -22915,15 +22942,15 @@
         <v>78</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22937,7 +22964,7 @@
         <v>89</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>78</v>
@@ -22946,18 +22973,18 @@
         <v>90</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N172" s="2"/>
-      <c r="O172" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>78</v>
       </c>
@@ -23005,7 +23032,7 @@
         <v>78</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -23032,15 +23059,15 @@
         <v>78</v>
       </c>
       <c r="AO172" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23054,7 +23081,7 @@
         <v>89</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>78</v>
@@ -23063,17 +23090,17 @@
         <v>90</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>78</v>
@@ -23122,7 +23149,7 @@
         <v>78</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -23149,15 +23176,15 @@
         <v>78</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23180,19 +23207,17 @@
         <v>90</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N174" s="2"/>
       <c r="O174" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>78</v>
@@ -23241,7 +23266,7 @@
         <v>78</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
@@ -23268,15 +23293,15 @@
         <v>78</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23299,19 +23324,19 @@
         <v>90</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>78</v>
@@ -23360,7 +23385,7 @@
         <v>78</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -23387,15 +23412,15 @@
         <v>78</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23406,7 +23431,7 @@
         <v>79</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>78</v>
@@ -23415,21 +23440,23 @@
         <v>78</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>684</v>
+        <v>103</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>685</v>
+        <v>307</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>686</v>
+        <v>308</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="O176" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O176" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P176" t="s" s="2">
         <v>78</v>
       </c>
@@ -23477,13 +23504,13 @@
         <v>78</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>683</v>
+        <v>311</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>78</v>
@@ -23504,15 +23531,15 @@
         <v>78</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23526,7 +23553,7 @@
         <v>80</v>
       </c>
       <c r="H177" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I177" t="s" s="2">
         <v>78</v>
@@ -23535,16 +23562,16 @@
         <v>78</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>277</v>
+        <v>690</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23570,29 +23597,31 @@
         <v>78</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>692</v>
+        <v>78</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>693</v>
+        <v>78</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AC177" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD177" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23610,28 +23639,26 @@
         <v>78</v>
       </c>
       <c r="AL177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO177" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="178" hidden="true">
+      <c r="A178" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="AM177" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO177" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s" s="2">
-        <v>695</v>
-      </c>
       <c r="B178" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="C178" t="s" s="2">
-        <v>696</v>
-      </c>
+        <v>694</v>
+      </c>
+      <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
         <v>78</v>
       </c>
@@ -23655,13 +23682,13 @@
         <v>277</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23687,29 +23714,29 @@
         <v>78</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y178" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="Y178" t="s" s="2">
+        <v>698</v>
+      </c>
       <c r="Z178" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="AC178" s="2"/>
       <c r="AD178" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23727,7 +23754,7 @@
         <v>78</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>78</v>
+        <v>700</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>78</v>
@@ -23739,14 +23766,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="C179" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>702</v>
+      </c>
       <c r="D179" t="s" s="2">
         <v>78</v>
       </c>
@@ -23755,10 +23784,10 @@
         <v>79</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>78</v>
@@ -23767,15 +23796,17 @@
         <v>78</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>104</v>
+        <v>695</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N179" s="2"/>
+        <v>696</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>697</v>
+      </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
         <v>78</v>
@@ -23800,13 +23831,11 @@
         <v>78</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y179" s="2"/>
       <c r="Z179" t="s" s="2">
-        <v>78</v>
+        <v>703</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>78</v>
@@ -23824,19 +23853,19 @@
         <v>78</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>106</v>
+        <v>694</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI179" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>78</v>
@@ -23856,21 +23885,21 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>78</v>
@@ -23882,17 +23911,15 @@
         <v>78</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>78</v>
@@ -23929,31 +23956,31 @@
         <v>78</v>
       </c>
       <c r="AB180" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC180" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD180" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE180" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>78</v>
@@ -23973,14 +24000,14 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
@@ -23996,23 +24023,21 @@
         <v>78</v>
       </c>
       <c r="J181" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>704</v>
+        <v>110</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>705</v>
+        <v>111</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
         <v>78</v>
       </c>
@@ -24048,19 +24073,19 @@
         <v>78</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
@@ -24072,7 +24097,7 @@
         <v>78</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>78</v>
@@ -24087,15 +24112,15 @@
         <v>78</v>
       </c>
       <c r="AO181" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24106,7 +24131,7 @@
         <v>79</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>78</v>
@@ -24115,19 +24140,23 @@
         <v>78</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>104</v>
+        <v>710</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N182" s="2"/>
-      <c r="O182" s="2"/>
+        <v>711</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>78</v>
       </c>
@@ -24175,19 +24204,19 @@
         <v>78</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI182" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>78</v>
@@ -24202,26 +24231,26 @@
         <v>78</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>78</v>
@@ -24233,17 +24262,15 @@
         <v>78</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>78</v>
@@ -24280,31 +24307,31 @@
         <v>78</v>
       </c>
       <c r="AB183" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC183" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD183" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE183" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI183" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>78</v>
@@ -24324,21 +24351,21 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>78</v>
@@ -24347,23 +24374,21 @@
         <v>78</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
         <v>78</v>
       </c>
@@ -24372,7 +24397,7 @@
         <v>78</v>
       </c>
       <c r="S184" t="s" s="2">
-        <v>712</v>
+        <v>78</v>
       </c>
       <c r="T184" t="s" s="2">
         <v>78</v>
@@ -24399,31 +24424,31 @@
         <v>78</v>
       </c>
       <c r="AB184" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC184" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE184" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ184" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK184" t="s" s="2">
         <v>78</v>
@@ -24438,15 +24463,15 @@
         <v>78</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24469,18 +24494,20 @@
         <v>90</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O185" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O185" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P185" t="s" s="2">
         <v>78</v>
       </c>
@@ -24489,7 +24516,7 @@
         <v>78</v>
       </c>
       <c r="S185" t="s" s="2">
-        <v>78</v>
+        <v>718</v>
       </c>
       <c r="T185" t="s" s="2">
         <v>78</v>
@@ -24528,7 +24555,7 @@
         <v>78</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
@@ -24555,15 +24582,15 @@
         <v>78</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24571,13 +24598,13 @@
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G186" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H186" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I186" t="s" s="2">
         <v>78</v>
@@ -24586,18 +24613,18 @@
         <v>90</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N186" s="2"/>
-      <c r="O186" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
         <v>78</v>
       </c>
@@ -24645,7 +24672,7 @@
         <v>78</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -24672,15 +24699,15 @@
         <v>78</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="187" hidden="true">
+    <row r="187">
       <c r="A187" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24688,13 +24715,13 @@
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G187" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H187" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I187" t="s" s="2">
         <v>78</v>
@@ -24703,17 +24730,17 @@
         <v>90</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>78</v>
@@ -24762,7 +24789,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -24789,15 +24816,15 @@
         <v>78</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24820,19 +24847,17 @@
         <v>90</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>78</v>
@@ -24881,7 +24906,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24908,15 +24933,15 @@
         <v>78</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24939,19 +24964,19 @@
         <v>90</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>78</v>
@@ -25000,7 +25025,7 @@
         <v>78</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -25027,19 +25052,17 @@
         <v>78</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="C190" t="s" s="2">
-        <v>724</v>
-      </c>
+        <v>728</v>
+      </c>
+      <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
         <v>78</v>
       </c>
@@ -25048,30 +25071,32 @@
         <v>79</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J190" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I190" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K190" t="s" s="2">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>689</v>
+        <v>307</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>690</v>
+        <v>308</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="O190" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O190" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P190" t="s" s="2">
         <v>78</v>
       </c>
@@ -25095,11 +25120,13 @@
         <v>78</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y190" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y190" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z190" t="s" s="2">
-        <v>725</v>
+        <v>78</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>78</v>
@@ -25117,13 +25144,13 @@
         <v>78</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>688</v>
+        <v>311</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI190" t="s" s="2">
         <v>78</v>
@@ -25144,17 +25171,19 @@
         <v>78</v>
       </c>
       <c r="AO190" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
-    <row r="191" hidden="true">
+    <row r="191">
       <c r="A191" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="C191" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>730</v>
+      </c>
       <c r="D191" t="s" s="2">
         <v>78</v>
       </c>
@@ -25163,10 +25192,10 @@
         <v>79</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>78</v>
@@ -25175,15 +25204,17 @@
         <v>78</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>104</v>
+        <v>695</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N191" s="2"/>
+        <v>696</v>
+      </c>
+      <c r="N191" t="s" s="2">
+        <v>697</v>
+      </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>78</v>
@@ -25208,13 +25239,11 @@
         <v>78</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>78</v>
+        <v>731</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>78</v>
@@ -25232,19 +25261,19 @@
         <v>78</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>106</v>
+        <v>694</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK191" t="s" s="2">
         <v>78</v>
@@ -25264,21 +25293,21 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>78</v>
@@ -25290,17 +25319,15 @@
         <v>78</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
         <v>78</v>
@@ -25337,31 +25364,31 @@
         <v>78</v>
       </c>
       <c r="AB192" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC192" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD192" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE192" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI192" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>78</v>
@@ -25381,14 +25408,14 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -25404,23 +25431,21 @@
         <v>78</v>
       </c>
       <c r="J193" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>729</v>
+        <v>110</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>730</v>
+        <v>111</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
         <v>78</v>
       </c>
@@ -25456,19 +25481,19 @@
         <v>78</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
@@ -25480,7 +25505,7 @@
         <v>78</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>78</v>
@@ -25495,15 +25520,15 @@
         <v>78</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25514,7 +25539,7 @@
         <v>79</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>78</v>
@@ -25523,19 +25548,23 @@
         <v>78</v>
       </c>
       <c r="J194" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>104</v>
+        <v>735</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N194" s="2"/>
-      <c r="O194" s="2"/>
+        <v>736</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P194" t="s" s="2">
         <v>78</v>
       </c>
@@ -25583,19 +25612,19 @@
         <v>78</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI194" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK194" t="s" s="2">
         <v>78</v>
@@ -25610,26 +25639,26 @@
         <v>78</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H195" t="s" s="2">
         <v>78</v>
@@ -25641,17 +25670,15 @@
         <v>78</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N195" s="2"/>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
         <v>78</v>
@@ -25688,31 +25715,31 @@
         <v>78</v>
       </c>
       <c r="AB195" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC195" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD195" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE195" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI195" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK195" t="s" s="2">
         <v>78</v>
@@ -25732,21 +25759,21 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>78</v>
@@ -25755,23 +25782,21 @@
         <v>78</v>
       </c>
       <c r="J196" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
         <v>78</v>
       </c>
@@ -25780,7 +25805,7 @@
         <v>78</v>
       </c>
       <c r="S196" t="s" s="2">
-        <v>734</v>
+        <v>78</v>
       </c>
       <c r="T196" t="s" s="2">
         <v>78</v>
@@ -25807,31 +25832,31 @@
         <v>78</v>
       </c>
       <c r="AB196" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC196" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD196" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE196" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI196" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK196" t="s" s="2">
         <v>78</v>
@@ -25846,15 +25871,15 @@
         <v>78</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25862,7 +25887,7 @@
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G197" t="s" s="2">
         <v>89</v>
@@ -25877,18 +25902,20 @@
         <v>90</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O197" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O197" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P197" t="s" s="2">
         <v>78</v>
       </c>
@@ -25897,7 +25924,7 @@
         <v>78</v>
       </c>
       <c r="S197" t="s" s="2">
-        <v>78</v>
+        <v>740</v>
       </c>
       <c r="T197" t="s" s="2">
         <v>78</v>
@@ -25936,7 +25963,7 @@
         <v>78</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>79</v>
@@ -25963,15 +25990,15 @@
         <v>78</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25979,7 +26006,7 @@
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G198" t="s" s="2">
         <v>89</v>
@@ -25994,18 +26021,18 @@
         <v>90</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N198" s="2"/>
-      <c r="O198" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N198" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
         <v>78</v>
       </c>
@@ -26053,7 +26080,7 @@
         <v>78</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
@@ -26080,15 +26107,15 @@
         <v>78</v>
       </c>
       <c r="AO198" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26096,7 +26123,7 @@
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G199" t="s" s="2">
         <v>89</v>
@@ -26111,17 +26138,17 @@
         <v>90</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>78</v>
@@ -26170,7 +26197,7 @@
         <v>78</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -26197,15 +26224,15 @@
         <v>78</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26228,19 +26255,17 @@
         <v>90</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N200" s="2"/>
       <c r="O200" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>78</v>
@@ -26289,7 +26314,7 @@
         <v>78</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
@@ -26316,15 +26341,15 @@
         <v>78</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26347,19 +26372,19 @@
         <v>90</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>78</v>
@@ -26408,7 +26433,7 @@
         <v>78</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
@@ -26435,15 +26460,15 @@
         <v>78</v>
       </c>
       <c r="AO201" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26454,7 +26479,7 @@
         <v>79</v>
       </c>
       <c r="G202" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H202" t="s" s="2">
         <v>78</v>
@@ -26463,20 +26488,22 @@
         <v>78</v>
       </c>
       <c r="J202" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>741</v>
+        <v>103</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>742</v>
+        <v>307</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="N202" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N202" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O202" t="s" s="2">
-        <v>744</v>
+        <v>310</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>78</v>
@@ -26525,13 +26552,13 @@
         <v>78</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>740</v>
+        <v>311</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH202" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI202" t="s" s="2">
         <v>78</v>
@@ -26552,15 +26579,15 @@
         <v>78</v>
       </c>
       <c r="AO202" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26583,16 +26610,18 @@
         <v>78</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>277</v>
+        <v>747</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="N203" s="2"/>
-      <c r="O203" s="2"/>
+      <c r="O203" t="s" s="2">
+        <v>750</v>
+      </c>
       <c r="P203" t="s" s="2">
         <v>78</v>
       </c>
@@ -26616,13 +26645,13 @@
         <v>78</v>
       </c>
       <c r="X203" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="Y203" t="s" s="2">
-        <v>748</v>
+        <v>78</v>
       </c>
       <c r="Z203" t="s" s="2">
-        <v>749</v>
+        <v>78</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>78</v>
@@ -26640,7 +26669,7 @@
         <v>78</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>79</v>
@@ -26670,12 +26699,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -26689,7 +26718,7 @@
         <v>80</v>
       </c>
       <c r="H204" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I204" t="s" s="2">
         <v>78</v>
@@ -26698,7 +26727,7 @@
         <v>78</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>751</v>
+        <v>277</v>
       </c>
       <c r="L204" t="s" s="2">
         <v>752</v>
@@ -26731,13 +26760,13 @@
         <v>78</v>
       </c>
       <c r="X204" t="s" s="2">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Y204" t="s" s="2">
-        <v>78</v>
+        <v>754</v>
       </c>
       <c r="Z204" t="s" s="2">
-        <v>78</v>
+        <v>755</v>
       </c>
       <c r="AA204" t="s" s="2">
         <v>78</v>
@@ -26755,7 +26784,7 @@
         <v>78</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>79</v>
@@ -26776,16 +26805,16 @@
         <v>78</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>754</v>
+        <v>78</v>
       </c>
       <c r="AN204" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO204" t="s" s="2">
-        <v>755</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="205" hidden="true">
+    <row r="205">
       <c r="A205" t="s" s="2">
         <v>756</v>
       </c>
@@ -26804,7 +26833,7 @@
         <v>80</v>
       </c>
       <c r="H205" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I205" t="s" s="2">
         <v>78</v>
@@ -26813,13 +26842,13 @@
         <v>78</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>583</v>
+        <v>757</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -26891,21 +26920,21 @@
         <v>78</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>78</v>
+        <v>760</v>
       </c>
       <c r="AN205" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO205" t="s" s="2">
-        <v>78</v>
+        <v>761</v>
       </c>
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -26916,7 +26945,7 @@
         <v>79</v>
       </c>
       <c r="G206" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H206" t="s" s="2">
         <v>78</v>
@@ -26928,13 +26957,13 @@
         <v>78</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>103</v>
+        <v>584</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>104</v>
+        <v>763</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>105</v>
+        <v>764</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -26985,19 +27014,19 @@
         <v>78</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>106</v>
+        <v>762</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI206" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK206" t="s" s="2">
         <v>78</v>
@@ -27017,21 +27046,21 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G207" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H207" t="s" s="2">
         <v>78</v>
@@ -27043,17 +27072,15 @@
         <v>78</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N207" s="2"/>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
         <v>78</v>
@@ -27102,19 +27129,19 @@
         <v>78</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH207" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI207" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK207" t="s" s="2">
         <v>78</v>
@@ -27134,14 +27161,14 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
-        <v>590</v>
+        <v>108</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
@@ -27154,26 +27181,24 @@
         <v>78</v>
       </c>
       <c r="I208" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J208" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K208" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>591</v>
+        <v>110</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>592</v>
+        <v>111</v>
       </c>
       <c r="N208" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="O208" t="s" s="2">
-        <v>340</v>
-      </c>
+      <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>78</v>
       </c>
@@ -27221,7 +27246,7 @@
         <v>78</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>593</v>
+        <v>116</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27253,42 +27278,46 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I209" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>277</v>
+        <v>109</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>763</v>
+        <v>592</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="N209" s="2"/>
-      <c r="O209" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="N209" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O209" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P209" t="s" s="2">
         <v>78</v>
       </c>
@@ -27312,13 +27341,13 @@
         <v>78</v>
       </c>
       <c r="X209" t="s" s="2">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>765</v>
+        <v>78</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>766</v>
+        <v>78</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>78</v>
@@ -27336,19 +27365,19 @@
         <v>78</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>762</v>
+        <v>594</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK209" t="s" s="2">
         <v>78</v>
@@ -27368,10 +27397,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27379,7 +27408,7 @@
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G210" t="s" s="2">
         <v>89</v>
@@ -27394,7 +27423,7 @@
         <v>78</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>768</v>
+        <v>277</v>
       </c>
       <c r="L210" t="s" s="2">
         <v>769</v>
@@ -27427,13 +27456,13 @@
         <v>78</v>
       </c>
       <c r="X210" t="s" s="2">
-        <v>78</v>
+        <v>168</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>78</v>
+        <v>771</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>78</v>
+        <v>772</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>78</v>
@@ -27451,10 +27480,10 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>89</v>
@@ -27483,10 +27512,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27494,10 +27523,10 @@
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>78</v>
@@ -27509,20 +27538,16 @@
         <v>78</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="N211" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="O211" t="s" s="2">
         <v>776</v>
       </c>
+      <c r="N211" s="2"/>
+      <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
         <v>78</v>
       </c>
@@ -27570,13 +27595,13 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="AG211" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>78</v>
@@ -27619,7 +27644,7 @@
         <v>80</v>
       </c>
       <c r="H212" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I212" t="s" s="2">
         <v>78</v>
@@ -27628,18 +27653,20 @@
         <v>78</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>277</v>
+        <v>778</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="O212" s="2"/>
+        <v>781</v>
+      </c>
+      <c r="O212" t="s" s="2">
+        <v>782</v>
+      </c>
       <c r="P212" t="s" s="2">
         <v>78</v>
       </c>
@@ -27663,26 +27690,28 @@
         <v>78</v>
       </c>
       <c r="X212" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="Y212" t="s" s="2">
-        <v>780</v>
+        <v>78</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>781</v>
+        <v>78</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB212" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AC212" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC212" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD212" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE212" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
         <v>777</v>
@@ -27715,16 +27744,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="C213" t="s" s="2">
         <v>783</v>
       </c>
+      <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
         <v>78</v>
       </c>
@@ -27754,7 +27781,7 @@
         <v>785</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
@@ -27783,28 +27810,26 @@
         <v>154</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB213" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC213" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="AC213" s="2"/>
       <c r="AD213" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE213" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
@@ -27834,14 +27859,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="214" hidden="true">
+    <row r="214">
       <c r="A214" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="C214" s="2"/>
+        <v>783</v>
+      </c>
+      <c r="C214" t="s" s="2">
+        <v>789</v>
+      </c>
       <c r="D214" t="s" s="2">
         <v>78</v>
       </c>
@@ -27850,10 +27877,10 @@
         <v>79</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H214" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I214" t="s" s="2">
         <v>78</v>
@@ -27862,15 +27889,17 @@
         <v>78</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>104</v>
+        <v>790</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N214" s="2"/>
+        <v>791</v>
+      </c>
+      <c r="N214" t="s" s="2">
+        <v>781</v>
+      </c>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -27895,13 +27924,13 @@
         <v>78</v>
       </c>
       <c r="X214" t="s" s="2">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>78</v>
+        <v>786</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>78</v>
+        <v>787</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>78</v>
@@ -27919,19 +27948,19 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>106</v>
+        <v>783</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH214" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI214" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ214" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK214" t="s" s="2">
         <v>78</v>
@@ -27951,21 +27980,21 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G215" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H215" t="s" s="2">
         <v>78</v>
@@ -27977,17 +28006,15 @@
         <v>78</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N215" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N215" s="2"/>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>78</v>
@@ -28024,31 +28051,31 @@
         <v>78</v>
       </c>
       <c r="AB215" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC215" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD215" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE215" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI215" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>78</v>
@@ -28068,14 +28095,14 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
@@ -28091,23 +28118,21 @@
         <v>78</v>
       </c>
       <c r="J216" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>283</v>
+        <v>110</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>284</v>
+        <v>111</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O216" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
         <v>78</v>
       </c>
@@ -28131,29 +28156,31 @@
         <v>78</v>
       </c>
       <c r="X216" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y216" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y216" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z216" t="s" s="2">
-        <v>792</v>
+        <v>78</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB216" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC216" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD216" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE216" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28165,7 +28192,7 @@
         <v>78</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK216" t="s" s="2">
         <v>78</v>
@@ -28180,15 +28207,15 @@
         <v>78</v>
       </c>
       <c r="AO216" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28199,7 +28226,7 @@
         <v>79</v>
       </c>
       <c r="G217" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H217" t="s" s="2">
         <v>78</v>
@@ -28208,19 +28235,23 @@
         <v>78</v>
       </c>
       <c r="J217" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>104</v>
+        <v>283</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N217" s="2"/>
-      <c r="O217" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N217" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O217" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
       </c>
@@ -28244,13 +28275,11 @@
         <v>78</v>
       </c>
       <c r="X217" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y217" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="Y217" s="2"/>
       <c r="Z217" t="s" s="2">
-        <v>78</v>
+        <v>798</v>
       </c>
       <c r="AA217" t="s" s="2">
         <v>78</v>
@@ -28268,19 +28297,19 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH217" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI217" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK217" t="s" s="2">
         <v>78</v>
@@ -28295,26 +28324,26 @@
         <v>78</v>
       </c>
       <c r="AO217" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E218" s="2"/>
       <c r="F218" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G218" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H218" t="s" s="2">
         <v>78</v>
@@ -28326,17 +28355,15 @@
         <v>78</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N218" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N218" s="2"/>
       <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
         <v>78</v>
@@ -28373,31 +28400,31 @@
         <v>78</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC218" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD218" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE218" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH218" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI218" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK218" t="s" s="2">
         <v>78</v>
@@ -28417,21 +28444,21 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H219" t="s" s="2">
         <v>78</v>
@@ -28440,23 +28467,21 @@
         <v>78</v>
       </c>
       <c r="J219" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O219" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
         <v>78</v>
       </c>
@@ -28492,31 +28517,31 @@
         <v>78</v>
       </c>
       <c r="AB219" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC219" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD219" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE219" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI219" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK219" t="s" s="2">
         <v>78</v>
@@ -28531,15 +28556,15 @@
         <v>78</v>
       </c>
       <c r="AO219" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -28562,18 +28587,20 @@
         <v>90</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O220" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O220" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P220" t="s" s="2">
         <v>78</v>
       </c>
@@ -28621,7 +28648,7 @@
         <v>78</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>79</v>
@@ -28648,15 +28675,15 @@
         <v>78</v>
       </c>
       <c r="AO220" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -28679,18 +28706,18 @@
         <v>90</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N221" s="2"/>
-      <c r="O221" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N221" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
         <v>78</v>
       </c>
@@ -28738,7 +28765,7 @@
         <v>78</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>79</v>
@@ -28753,7 +28780,7 @@
         <v>101</v>
       </c>
       <c r="AK221" t="s" s="2">
-        <v>803</v>
+        <v>78</v>
       </c>
       <c r="AL221" t="s" s="2">
         <v>78</v>
@@ -28765,15 +28792,15 @@
         <v>78</v>
       </c>
       <c r="AO221" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -28796,17 +28823,17 @@
         <v>90</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>78</v>
@@ -28855,7 +28882,7 @@
         <v>78</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>79</v>
@@ -28870,7 +28897,7 @@
         <v>101</v>
       </c>
       <c r="AK222" t="s" s="2">
-        <v>78</v>
+        <v>809</v>
       </c>
       <c r="AL222" t="s" s="2">
         <v>78</v>
@@ -28882,15 +28909,15 @@
         <v>78</v>
       </c>
       <c r="AO222" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -28913,19 +28940,17 @@
         <v>90</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N223" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N223" s="2"/>
       <c r="O223" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>78</v>
@@ -28974,7 +28999,7 @@
         <v>78</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>79</v>
@@ -29001,15 +29026,15 @@
         <v>78</v>
       </c>
       <c r="AO223" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29032,19 +29057,19 @@
         <v>90</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O224" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>78</v>
@@ -29093,7 +29118,7 @@
         <v>78</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>79</v>
@@ -29120,19 +29145,17 @@
         <v>78</v>
       </c>
       <c r="AO224" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="C225" t="s" s="2">
-        <v>811</v>
-      </c>
+        <v>815</v>
+      </c>
+      <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
         <v>78</v>
       </c>
@@ -29141,30 +29164,32 @@
         <v>79</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I225" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J225" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I225" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J225" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K225" t="s" s="2">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>812</v>
+        <v>307</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>813</v>
+        <v>308</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="O225" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O225" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P225" t="s" s="2">
         <v>78</v>
       </c>
@@ -29188,13 +29213,13 @@
         <v>78</v>
       </c>
       <c r="X225" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="Y225" t="s" s="2">
-        <v>780</v>
+        <v>78</v>
       </c>
       <c r="Z225" t="s" s="2">
-        <v>781</v>
+        <v>78</v>
       </c>
       <c r="AA225" t="s" s="2">
         <v>78</v>
@@ -29212,13 +29237,13 @@
         <v>78</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>777</v>
+        <v>311</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH225" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI225" t="s" s="2">
         <v>78</v>
@@ -29239,17 +29264,19 @@
         <v>78</v>
       </c>
       <c r="AO225" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
-    <row r="226" hidden="true">
+    <row r="226">
       <c r="A226" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="C226" s="2"/>
+        <v>783</v>
+      </c>
+      <c r="C226" t="s" s="2">
+        <v>817</v>
+      </c>
       <c r="D226" t="s" s="2">
         <v>78</v>
       </c>
@@ -29258,10 +29285,10 @@
         <v>79</v>
       </c>
       <c r="G226" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H226" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I226" t="s" s="2">
         <v>78</v>
@@ -29270,15 +29297,17 @@
         <v>78</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>104</v>
+        <v>818</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N226" s="2"/>
+        <v>819</v>
+      </c>
+      <c r="N226" t="s" s="2">
+        <v>781</v>
+      </c>
       <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
         <v>78</v>
@@ -29303,13 +29332,13 @@
         <v>78</v>
       </c>
       <c r="X226" t="s" s="2">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Y226" t="s" s="2">
-        <v>78</v>
+        <v>786</v>
       </c>
       <c r="Z226" t="s" s="2">
-        <v>78</v>
+        <v>787</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>78</v>
@@ -29327,19 +29356,19 @@
         <v>78</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>106</v>
+        <v>783</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH226" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI226" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ226" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK226" t="s" s="2">
         <v>78</v>
@@ -29359,21 +29388,21 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E227" s="2"/>
       <c r="F227" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G227" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H227" t="s" s="2">
         <v>78</v>
@@ -29385,17 +29414,15 @@
         <v>78</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N227" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N227" s="2"/>
       <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
         <v>78</v>
@@ -29432,31 +29459,31 @@
         <v>78</v>
       </c>
       <c r="AB227" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC227" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD227" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE227" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH227" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI227" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ227" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK227" t="s" s="2">
         <v>78</v>
@@ -29476,14 +29503,14 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" t="s" s="2">
@@ -29499,23 +29526,21 @@
         <v>78</v>
       </c>
       <c r="J228" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>283</v>
+        <v>110</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>284</v>
+        <v>111</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O228" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
         <v>78</v>
       </c>
@@ -29539,29 +29564,31 @@
         <v>78</v>
       </c>
       <c r="X228" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y228" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y228" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z228" t="s" s="2">
-        <v>817</v>
+        <v>78</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB228" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC228" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD228" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE228" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>79</v>
@@ -29573,7 +29600,7 @@
         <v>78</v>
       </c>
       <c r="AJ228" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK228" t="s" s="2">
         <v>78</v>
@@ -29588,15 +29615,15 @@
         <v>78</v>
       </c>
       <c r="AO228" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -29607,7 +29634,7 @@
         <v>79</v>
       </c>
       <c r="G229" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H229" t="s" s="2">
         <v>78</v>
@@ -29616,19 +29643,23 @@
         <v>78</v>
       </c>
       <c r="J229" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>104</v>
+        <v>283</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N229" s="2"/>
-      <c r="O229" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N229" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O229" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P229" t="s" s="2">
         <v>78</v>
       </c>
@@ -29652,13 +29683,11 @@
         <v>78</v>
       </c>
       <c r="X229" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y229" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="Y229" s="2"/>
       <c r="Z229" t="s" s="2">
-        <v>78</v>
+        <v>823</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>78</v>
@@ -29676,19 +29705,19 @@
         <v>78</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH229" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI229" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ229" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK229" t="s" s="2">
         <v>78</v>
@@ -29703,26 +29732,26 @@
         <v>78</v>
       </c>
       <c r="AO229" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G230" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H230" t="s" s="2">
         <v>78</v>
@@ -29734,17 +29763,15 @@
         <v>78</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N230" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N230" s="2"/>
       <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
         <v>78</v>
@@ -29781,31 +29808,31 @@
         <v>78</v>
       </c>
       <c r="AB230" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC230" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD230" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE230" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI230" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ230" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK230" t="s" s="2">
         <v>78</v>
@@ -29825,21 +29852,21 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G231" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H231" t="s" s="2">
         <v>78</v>
@@ -29848,23 +29875,21 @@
         <v>78</v>
       </c>
       <c r="J231" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O231" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
         <v>78</v>
       </c>
@@ -29900,31 +29925,31 @@
         <v>78</v>
       </c>
       <c r="AB231" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC231" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD231" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE231" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH231" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI231" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ231" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK231" t="s" s="2">
         <v>78</v>
@@ -29939,15 +29964,15 @@
         <v>78</v>
       </c>
       <c r="AO231" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -29970,18 +29995,20 @@
         <v>90</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O232" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O232" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P232" t="s" s="2">
         <v>78</v>
       </c>
@@ -30029,7 +30056,7 @@
         <v>78</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>79</v>
@@ -30056,15 +30083,15 @@
         <v>78</v>
       </c>
       <c r="AO232" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30087,18 +30114,18 @@
         <v>90</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N233" s="2"/>
-      <c r="O233" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N233" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O233" s="2"/>
       <c r="P233" t="s" s="2">
         <v>78</v>
       </c>
@@ -30146,7 +30173,7 @@
         <v>78</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>79</v>
@@ -30161,7 +30188,7 @@
         <v>101</v>
       </c>
       <c r="AK233" t="s" s="2">
-        <v>823</v>
+        <v>78</v>
       </c>
       <c r="AL233" t="s" s="2">
         <v>78</v>
@@ -30173,15 +30200,15 @@
         <v>78</v>
       </c>
       <c r="AO233" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30204,17 +30231,17 @@
         <v>90</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>78</v>
@@ -30263,7 +30290,7 @@
         <v>78</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>79</v>
@@ -30278,7 +30305,7 @@
         <v>101</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>78</v>
+        <v>829</v>
       </c>
       <c r="AL234" t="s" s="2">
         <v>78</v>
@@ -30290,15 +30317,15 @@
         <v>78</v>
       </c>
       <c r="AO234" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30321,19 +30348,17 @@
         <v>90</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N235" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N235" s="2"/>
       <c r="O235" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>78</v>
@@ -30382,7 +30407,7 @@
         <v>78</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>79</v>
@@ -30409,15 +30434,15 @@
         <v>78</v>
       </c>
       <c r="AO235" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30440,19 +30465,19 @@
         <v>90</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O236" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P236" t="s" s="2">
         <v>78</v>
@@ -30501,7 +30526,7 @@
         <v>78</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>79</v>
@@ -30528,11 +30553,130 @@
         <v>78</v>
       </c>
       <c r="AO236" t="s" s="2">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="237" hidden="true">
+      <c r="A237" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="C237" s="2"/>
+      <c r="D237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E237" s="2"/>
+      <c r="F237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G237" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J237" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K237" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L237" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M237" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N237" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O237" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="P237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q237" s="2"/>
+      <c r="R237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF237" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AG237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH237" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ237" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN237" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO237" t="s" s="2">
         <v>312</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO236">
+  <autoFilter ref="A1:AO237">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -30542,7 +30686,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI235">
+  <conditionalFormatting sqref="A2:AI236">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
